--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487653_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487653_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4991</v>
+        <v>3.8073</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0486</v>
+        <v>4.2478</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5495</v>
+        <v>-0.4405</v>
       </c>
       <c r="G2" t="n">
         <v>2.9611</v>
@@ -610,13 +610,13 @@
         <v>0.9702</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8499</v>
+        <v>0.1581</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6079</v>
+        <v>-0.1929</v>
       </c>
       <c r="U2" t="n">
-        <v>0.242</v>
+        <v>0.3511</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2821</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.819</v>
+        <v>2.764</v>
       </c>
       <c r="E3" t="n">
-        <v>3.987</v>
+        <v>3.6867</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.168</v>
+        <v>-0.9227</v>
       </c>
       <c r="G3" t="n">
         <v>6.2417</v>
@@ -688,13 +688,13 @@
         <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.6553</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3017</v>
+        <v>-0.602</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2985</v>
+        <v>-0.0532</v>
       </c>
       <c r="V3" t="n">
         <v>0.2821</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1803</v>
+        <v>1.0712</v>
       </c>
       <c r="E4" t="n">
         <v>-0.0131</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1933</v>
+        <v>1.0843</v>
       </c>
       <c r="G4" t="n">
         <v>-2.4862</v>
@@ -766,13 +766,13 @@
         <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4724</v>
+        <v>0.3634</v>
       </c>
       <c r="T4" t="n">
         <v>0.0011</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4713</v>
+        <v>0.3623</v>
       </c>
       <c r="V4" t="n">
         <v>1.8358</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1216</v>
+        <v>0.958</v>
       </c>
       <c r="E5" t="n">
         <v>1.9448</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8232</v>
+        <v>-0.9867</v>
       </c>
       <c r="G5" t="n">
         <v>0.5038</v>
@@ -844,13 +844,13 @@
         <v>0.3881</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2297</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2297</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5673</v>
+        <v>-0.7219</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4651</v>
+        <v>2.365</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.0324</v>
+        <v>-3.0869</v>
       </c>
       <c r="G6" t="n">
         <v>-2.9153</v>
@@ -922,13 +922,13 @@
         <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2183</v>
+        <v>0.0636</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.12</v>
+        <v>-0.2201</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3383</v>
+        <v>0.2838</v>
       </c>
       <c r="V6" t="n">
         <v>3.294</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ALMENARA SANABRIAS</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0773</v>
+        <v>-1.0031</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.806</v>
+        <v>0.0988</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2713</v>
+        <v>-1.1019</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7058</v>
+        <v>0.6828</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5174</v>
+        <v>0.6995</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1884</v>
+        <v>-0.0167</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5032</v>
+        <v>1.0504</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1236</v>
+        <v>1.0504</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6267</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2027</v>
+        <v>-0.3677</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.641</v>
+        <v>-0.351</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5617</v>
+        <v>-0.0167</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
         <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6133</v>
+        <v>-0.1217</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3028</v>
+        <v>0.0185</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3104</v>
+        <v>-0.1402</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6597</v>
+        <v>-1.1761</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6597</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>A. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2578</v>
+        <v>-1.05</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1014</v>
+        <v>-0.806</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1564</v>
+        <v>-0.2441</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6828</v>
+        <v>-1.7058</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6995</v>
+        <v>-0.5174</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0167</v>
+        <v>-1.1884</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0504</v>
+        <v>-0.5032</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0504</v>
+        <v>0.1236</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.6267</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3677</v>
+        <v>-1.2027</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.351</v>
+        <v>-0.641</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0167</v>
+        <v>-0.5617</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.5821</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3764</v>
+        <v>-0.586</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1817</v>
+        <v>-0.3028</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1947</v>
+        <v>-0.2832</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1761</v>
+        <v>0.6597</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1761</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2401</v>
+        <v>-3.4125</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7598</v>
+        <v>-2.6597</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4802</v>
+        <v>-0.7528</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7237</v>
@@ -1156,13 +1156,13 @@
         <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1581</v>
+        <v>-0.3306</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7874</v>
+        <v>-0.6873</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6292</v>
+        <v>0.3567</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4412</v>
+        <v>-4.4769</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2725</v>
+        <v>-3.8721</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1687</v>
+        <v>-0.6047</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0765</v>
@@ -1234,13 +1234,13 @@
         <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2174</v>
+        <v>0.1817</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2113</v>
+        <v>-0.8109</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4287</v>
+        <v>0.9926</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2239</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1181</v>
+        <v>-5.9545</v>
       </c>
       <c r="E11" t="n">
         <v>-1.6203</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4978</v>
+        <v>-4.3343</v>
       </c>
       <c r="G11" t="n">
         <v>-4.5617</v>
@@ -1312,13 +1312,13 @@
         <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2795</v>
+        <v>0.443</v>
       </c>
       <c r="T11" t="n">
         <v>-0.3017</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5812</v>
+        <v>0.7447</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8358</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.8949</v>
+        <v>-10.9583</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.2113</v>
+        <v>-7.7108</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6836</v>
+        <v>-3.2475</v>
       </c>
       <c r="G12" t="n">
         <v>-10.2483</v>
@@ -1390,13 +1390,13 @@
         <v>1.1642</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2481</v>
+        <v>-0.3115</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2719</v>
+        <v>-0.7714</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0238</v>
+        <v>0.4599</v>
       </c>
       <c r="V12" t="n">
         <v>0.3776</v>
@@ -1426,7 +1426,7 @@
         <v>-18.9767</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.338899999999998</v>
+        <v>-4.3389</v>
       </c>
       <c r="F13" t="n">
         <v>-14.6378</v>
@@ -1438,7 +1438,7 @@
         <v>-11.213</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.1154</v>
+        <v>-4.115400000000001</v>
       </c>
       <c r="J13" t="n">
         <v>7.0548</v>
@@ -1468,13 +1468,13 @@
         <v>10.6719</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.729</v>
+        <v>-0.7291000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>-3.8695</v>
       </c>
       <c r="U13" t="n">
-        <v>3.1406</v>
+        <v>3.1407</v>
       </c>
       <c r="V13" t="n">
         <v>1.9313</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5482</v>
+        <v>5.7211</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5669</v>
+        <v>3.7671</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9813</v>
+        <v>1.954</v>
       </c>
       <c r="G14" t="n">
         <v>6.6487</v>
@@ -1546,13 +1546,13 @@
         <v>1.5523</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1886</v>
+        <v>-0.0157</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5451</v>
+        <v>-0.3449</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3565</v>
+        <v>0.3292</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3299</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6599</v>
+        <v>4.5048</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6695</v>
+        <v>4.2691</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0097</v>
+        <v>0.2356</v>
       </c>
       <c r="G15" t="n">
         <v>2.1121</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3104</v>
+        <v>0.1553</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2445</v>
+        <v>-0.1559</v>
       </c>
       <c r="U15" t="n">
-        <v>0.066</v>
+        <v>0.3113</v>
       </c>
       <c r="V15" t="n">
         <v>2.0433</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2672</v>
+        <v>3.0397</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4061</v>
+        <v>2.2059</v>
       </c>
       <c r="F16" t="n">
-        <v>0.861</v>
+        <v>0.8338</v>
       </c>
       <c r="G16" t="n">
         <v>4.008</v>
@@ -1702,13 +1702,13 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2488</v>
+        <v>0.0213</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2412</v>
+        <v>-0.4414</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4899</v>
+        <v>0.4627</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9896</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7467</v>
+        <v>2.8557</v>
       </c>
       <c r="E17" t="n">
         <v>3.1747</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.428</v>
+        <v>-0.3189</v>
       </c>
       <c r="G17" t="n">
         <v>2.6828</v>
@@ -1780,13 +1780,13 @@
         <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3519</v>
+        <v>0.461</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4114</v>
+        <v>0.5204</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0642</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0088</v>
+        <v>1.8863</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8095</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8007</v>
+        <v>1.2255</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7691</v>
+        <v>-0.5831</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0589</v>
+        <v>0.5141</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2897</v>
+        <v>-1.0972</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3833</v>
+        <v>1.0052</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9289</v>
+        <v>1.5407</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5455</v>
+        <v>-0.5355</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6142</v>
+        <v>-1.5883</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.87</v>
+        <v>-1.0266</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2558</v>
+        <v>-0.5617</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9702</v>
+        <v>2.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8979</v>
+        <v>0.2336</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4262</v>
+        <v>-0.6862</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4718</v>
+        <v>0.9197</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.6283</v>
+        <v>0.4895</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6283</v>
+        <v>-1.0164</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>G. MATÍAS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0043</v>
+        <v>1.4731</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5607</v>
+        <v>1.2791</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4436</v>
+        <v>0.194</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5831</v>
+        <v>1.2791</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5141</v>
+        <v>0.0206</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0972</v>
+        <v>1.2585</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0052</v>
+        <v>1.2791</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5407</v>
+        <v>0.0206</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5355</v>
+        <v>1.2585</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5883</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0266</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5617</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7463</v>
+        <v>0.194</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9105</v>
+        <v>0.194</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3515</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1378</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4895</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. MATÍAS RODRÍGUEZ</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4731</v>
+        <v>1.4538</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2791</v>
+        <v>2.309</v>
       </c>
       <c r="F20" t="n">
-        <v>0.194</v>
+        <v>-0.8552</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2791</v>
+        <v>1.7691</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0206</v>
+        <v>2.0589</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2585</v>
+        <v>-0.2897</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2791</v>
+        <v>2.3833</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0206</v>
+        <v>2.9289</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2585</v>
+        <v>-0.5455</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-0.6142</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.2558</v>
       </c>
       <c r="P20" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.3429</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.0743</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.4172</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.6283</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.6283</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3929</v>
+        <v>0.8389</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5487</v>
+        <v>-0.0482</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9416</v>
+        <v>0.8871</v>
       </c>
       <c r="G21" t="n">
         <v>2.1892</v>
@@ -2092,13 +2092,13 @@
         <v>1.9403</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.0636</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8479</v>
+        <v>-0.3474</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3383</v>
+        <v>0.2838</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1224</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6783</v>
+        <v>-0.5604</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0311</v>
+        <v>-1.1312</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3528</v>
+        <v>0.5708</v>
       </c>
       <c r="G22" t="n">
         <v>-3.689</v>
@@ -2170,13 +2170,13 @@
         <v>1.7463</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2416</v>
+        <v>-0.1237</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4229</v>
+        <v>-0.523</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1813</v>
+        <v>0.3993</v>
       </c>
       <c r="V22" t="n">
         <v>1.506</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.446</v>
+        <v>-2.2364</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.249</v>
+        <v>-1.8486</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.197</v>
+        <v>-0.3878</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0887</v>
@@ -2248,13 +2248,13 @@
         <v>1.9403</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4917</v>
+        <v>-0.2821</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9085</v>
+        <v>-0.5081</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4168</v>
+        <v>0.226</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8358</v>
@@ -2281,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>18.9768</v>
+        <v>18.9766</v>
       </c>
       <c r="E24" t="n">
         <v>14.6377</v>
@@ -2326,13 +2326,13 @@
         <v>15.5227</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7289999999999999</v>
+        <v>0.7290000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-3.1407</v>
       </c>
       <c r="U24" t="n">
-        <v>3.8698</v>
+        <v>3.8696</v>
       </c>
       <c r="V24" t="n">
         <v>-1.9314</v>
